--- a/BOM_neopixel-seven-segment-display.xlsx
+++ b/BOM_neopixel-seven-segment-display.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="62">
   <si>
     <t>No.</t>
   </si>
@@ -106,43 +106,40 @@
     <t>4</t>
   </si>
   <si>
-    <t>1770995</t>
+    <t>DB2EVC-2.54-6P-GN</t>
   </si>
   <si>
     <t>H1,H2</t>
   </si>
   <si>
-    <t>CONN_1814605</t>
+    <t>CONN-TH_6P-P2.54_DIBO_DB2EVC-2.54-6P-GN</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Phoenix Contact</t>
-  </si>
-  <si>
-    <t>277-2090-1-ND</t>
-  </si>
-  <si>
-    <t>DigiKey</t>
+    <t>DORABO(地博电气)</t>
+  </si>
+  <si>
+    <t>C2927497</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>PZ254V-11-02P</t>
+    <t>DSWB01LHGET</t>
   </si>
   <si>
     <t>J1</t>
   </si>
   <si>
-    <t>HDR-TH_2P-P2.54-V-M</t>
-  </si>
-  <si>
-    <t>XFCN(兴飞)</t>
-  </si>
-  <si>
-    <t>C492401</t>
+    <t>SW-TH_DSWB01LHGET</t>
+  </si>
+  <si>
+    <t>YE</t>
+  </si>
+  <si>
+    <t>C126888</t>
   </si>
   <si>
     <t>6</t>
@@ -739,36 +736,36 @@
         <v>36</v>
       </c>
       <c r="J5" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
         <v>39</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>40</v>
-      </c>
-      <c r="E6" t="s">
-        <v>41</v>
       </c>
       <c r="F6" t="s">
         <v>34</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" t="s">
         <v>42</v>
-      </c>
-      <c r="I6" t="s">
-        <v>43</v>
       </c>
       <c r="J6" t="s">
         <v>17</v>
@@ -776,31 +773,31 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" t="s">
         <v>45</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>46</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" t="s">
         <v>47</v>
       </c>
-      <c r="F7" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>48</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>49</v>
-      </c>
-      <c r="I7" t="s">
-        <v>50</v>
       </c>
       <c r="J7" t="s">
         <v>17</v>
@@ -808,31 +805,31 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B8">
         <v>63</v>
       </c>
       <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
         <v>52</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>53</v>
-      </c>
-      <c r="E8" t="s">
-        <v>54</v>
       </c>
       <c r="F8" t="s">
         <v>34</v>
       </c>
       <c r="G8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" t="s">
         <v>55</v>
-      </c>
-      <c r="I8" t="s">
-        <v>56</v>
       </c>
       <c r="J8" t="s">
         <v>17</v>
@@ -840,31 +837,31 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" t="s">
         <v>58</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>59</v>
-      </c>
-      <c r="E9" t="s">
-        <v>60</v>
       </c>
       <c r="F9" t="s">
         <v>34</v>
       </c>
       <c r="G9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H9" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" t="s">
         <v>61</v>
-      </c>
-      <c r="I9" t="s">
-        <v>62</v>
       </c>
       <c r="J9" t="s">
         <v>17</v>
